--- a/stories/arbres/ATOM-JEU.BAL.001-03.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sacha est au parc avec papa. Papa montre un cercle d'herbe. Papa dit : c'est l'espace du jeu. On reste dans l'espace du jeu. Sacha a un ballon rouge. Papa dit : chacun a un tour. On se passe le ballon. Sacha passe le ballon à Lina. Lina le passe à papa. C'est le tour de Sacha. Il reste dans l'espace du jeu. Plus tard, au jardin, papa pose deux sacs. C'est l'espace du jeu. Sacha se souvient. Il passe le ballon. Il attend son tour. Puis il joue. Les pieds restent dans l'espace du jeu. Même leçon, autre lieu. Passer. Un tour. L'espace du jeu.</t>
+          <t>Sacha est au parc avec papa. Papa montre un cercle d'herbe. C'est l'espace du jeu. On reste dans l'espace du jeu. Sacha a un ballon rouge. Chacun a un tour. On se passe le ballon. Sacha passe le ballon à Lina. Lina le passe à papa. C'est le tour de Sacha. Il reste dans l'espace du jeu. Plus tard, au jardin, papa pose deux sacs. C'est l'espace du jeu. Sacha se souvient. Il passe le ballon. Il attend son tour. Puis il joue. Les pieds restent dans l'espace du jeu. Même leçon, autre lieu. Passer. Un tour. L'espace du jeu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Sacha est au parc avec papa. Papa montre un cercle d'herbe.
+papa|C'est l'espace du jeu. On reste dans l'espace du jeu.
+narrateur|Sacha a un ballon rouge.
+papa|Chacun a un tour. On se passe le ballon.
+narrateur|Sacha passe le ballon à Lina. Lina le passe à papa. C'est le tour de Sacha. Il reste dans l'espace du jeu. Plus tard, au jardin, papa pose deux sacs. C'est l'espace du jeu. Sacha se souvient. Il passe le ballon. Il attend son tour. Puis il joue. Les pieds restent dans l'espace du jeu. Même leçon, autre lieu. Passer. Un tour. L'espace du jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Sacha a le ballon. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Sacha a passé le ballon. Au parc, puis au jardin. Dans l'espace du jeu. Chacun a eu un tour.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1826,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Sacha pose le ballon. Papa range les sacs.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1993,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2033,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.BAL.001-03.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Sacha passe le ballon à Lina. Lina le passe à papa. C'est le tour de Sacha. Il reste dans l'espace du jeu. Plus tard, au jardin, papa pose deux sacs. C'est l'espace du jeu. Sacha se souvient. Il passe le ballon. Il attend son tour. Puis il joue. Les pieds restent dans l'espace du jeu. Même leçon, autre lieu. Passer. Un tour. L'espace du jeu.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1507,7 @@
           <t>narrateur|Sacha a le ballon. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1679,11 @@
           <t>narrateur|Sacha a passé le ballon. Au parc, puis au jardin. Dans l'espace du jeu. Chacun a eu un tour.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1831,6 +1847,7 @@
           <t>narrateur|Sacha pose le ballon. Papa range les sacs.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1998,6 +2015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2016,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2040,6 +2058,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2241,6 +2273,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-JEU.BAL.001-03.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sacha passe le ballon, deux espaces</t>
+          <t>Nino passe le ballon, deux espaces</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le ballon rouge s'appuie contre la palissade. Au parc puis au jardin, Nino passe, attend, reste dans l'espace du jeu. Nina, papa et maman aussi.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sacha est au parc avec papa. Papa montre un cercle d'herbe. C'est l'espace du jeu. On reste dans l'espace du jeu. Sacha a un ballon rouge. Chacun a un tour. On se passe le ballon. Sacha passe le ballon à Lina. Lina le passe à papa. C'est le tour de Sacha. Il reste dans l'espace du jeu. Plus tard, au jardin, papa pose deux sacs. C'est l'espace du jeu. Sacha se souvient. Il passe le ballon. Il attend son tour. Puis il joue. Les pieds restent dans l'espace du jeu. Même leçon, autre lieu. Passer. Un tour. L'espace du jeu.</t>
+          <t>Le ballon rouge s'appuie contre la palissade. Le bois est chaud au soleil. Au loin, un chien dit wouaf, une fois. Les feuilles bougent. Papa marche sur l'herbe courte. Nina attend près du banc. Maman pose la gourde à l'ombre. Nino, tu vois le ballon ? Oui, papa. Il est rouge. Il attend contre le bois. Il est tout chaud, ce bois. En ce moment, papa montre un cercle d'herbe. C'est l'espace du jeu. On reste dans l'espace du jeu. Nino a le ballon rouge. Le grain du ballon pique un peu. Chacun a un tour. On se passe le ballon. Nino passe le ballon à Nina. Nina le passe à papa. C'est le tour de Nino. Il reste dans l'espace du jeu. Bien joué. Chacun a un tour. C'est ton tour, Nino. Je passe. Nino passe encore. Les pieds restent dans l'herbe du cercle. Vous restez dans l'espace. Plus tard, au jardin, papa pose deux sacs. Maman ouvre le portillon. C'est l'espace du jeu. Nino se souvient. Il passe le ballon. Il attend son tour. Puis il joue. Les pieds restent dans l'espace du jeu. Au parc, puis au jardin. Passer. Un tour. L'espace du jeu. Un tour. L'espace du jeu. Chacun a un tour. Bravo, Nino. Bravo, Nina. Vous avez fait du bon travail. Le ballon rouge n'est plus contre la palissade. Il voyage entre les mains.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,11 +1324,56 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Sacha est au parc avec papa. Papa montre un cercle d'herbe.
-papa|C'est l'espace du jeu. On reste dans l'espace du jeu.
-narrateur|Sacha a un ballon rouge.
-papa|Chacun a un tour. On se passe le ballon.
-narrateur|Sacha passe le ballon à Lina. Lina le passe à papa. C'est le tour de Sacha. Il reste dans l'espace du jeu. Plus tard, au jardin, papa pose deux sacs. C'est l'espace du jeu. Sacha se souvient. Il passe le ballon. Il attend son tour. Puis il joue. Les pieds restent dans l'espace du jeu. Même leçon, autre lieu. Passer. Un tour. L'espace du jeu.</t>
+          <t>narrateur|Le ballon rouge s'appuie contre la palissade.
+narrateur|Le bois est chaud au soleil.
+narrateur|Au loin, un chien dit wouaf, une fois.
+narrateur|Les feuilles bougent.
+narrateur|Papa marche sur l'herbe courte.
+narrateur|Nina attend près du banc.
+narrateur|Maman pose la gourde à l'ombre.
+papa|Nino, tu vois le ballon ?
+enfant-m|Oui, papa.
+enfant-m|Il est rouge.
+papa|Il attend contre le bois.
+maman|Il est tout chaud, ce bois.
+narrateur|En ce moment, papa montre un cercle d'herbe.
+papa|C'est l'espace du jeu.
+papa|On reste dans l'espace du jeu.
+narrateur|Nino a le ballon rouge.
+narrateur|Le grain du ballon pique un peu.
+papa|Chacun a un tour.
+papa|On se passe le ballon.
+narrateur|Nino passe le ballon à Nina.
+narrateur|Nina le passe à papa.
+narrateur|C'est le tour de Nino.
+narrateur|Il reste dans l'espace du jeu.
+papa|Bien joué.
+papa|Chacun a un tour.
+enfant-f|C'est ton tour, Nino.
+enfant-m|Je passe.
+narrateur|Nino passe encore.
+narrateur|Les pieds restent dans l'herbe du cercle.
+maman|Vous restez dans l'espace.
+narrateur|Plus tard, au jardin, papa pose deux sacs.
+narrateur|Maman ouvre le portillon.
+papa|C'est l'espace du jeu.
+narrateur|Nino se souvient.
+narrateur|Il passe le ballon.
+narrateur|Il attend son tour.
+narrateur|Puis il joue.
+narrateur|Les pieds restent dans l'espace du jeu.
+papa|Au parc, puis au jardin.
+papa|Passer.
+papa|Un tour.
+papa|L'espace du jeu.
+enfant-m|Un tour.
+enfant-f|L'espace du jeu.
+maman|Chacun a un tour.
+papa|Bravo, Nino.
+papa|Bravo, Nina.
+papa|Vous avez fait du bon travail.
+narrateur|Le ballon rouge n'est plus contre la palissade.
+narrateur|Il voyage entre les mains.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1348,7 +1405,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Sacha a le ballon. Que fait-il ?</t>
+          <t>Nino a le ballon. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,10 +1561,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Sacha a le ballon. Que fait-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Nino a le ballon.
+narrateur|Que fait-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1532,7 +1589,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sacha a passé le ballon. Au parc, puis au jardin. Dans l'espace du jeu. Chacun a eu un tour.</t>
+          <t>Nino a passé le ballon. Au parc, puis au jardin. Dans l'espace du jeu. Chacun a eu un tour. Tu as attendu ton tour ? Oui, papa. Moi aussi. Bravo. On reste dans l'espace du jeu. Nina, tu as passé aussi ? Oui, maman. Bravo. L'herbe du jardin sent la menthe. Les sacs marquent encore le cercle.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,7 +1733,20 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sacha a passé le ballon. Au parc, puis au jardin. Dans l'espace du jeu. Chacun a eu un tour.</t>
+          <t>narrateur|Nino a passé le ballon.
+narrateur|Au parc, puis au jardin.
+narrateur|Dans l'espace du jeu.
+narrateur|Chacun a eu un tour.
+papa|Tu as attendu ton tour ?
+enfant-m|Oui, papa.
+enfant-f|Moi aussi.
+papa|Bravo.
+papa|On reste dans l'espace du jeu.
+maman|Nina, tu as passé aussi ?
+enfant-f|Oui, maman.
+maman|Bravo.
+narrateur|L'herbe du jardin sent la menthe.
+narrateur|Les sacs marquent encore le cercle.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1708,7 +1778,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Sacha pose le ballon. Papa range les sacs.</t>
+          <t>Nino pose le ballon. Je range les sacs. Papa range les sacs. Vous avez fini de jouer ? Oui, papa. Oui. Bravo. On boit une gorgée ? Oui, maman. La gourde est fraîche, à l'ombre. Le bois de la palissade est encore chaud.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1844,10 +1914,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Sacha pose le ballon. Papa range les sacs.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Nino pose le ballon.
+papa|Je range les sacs.
+narrateur|Papa range les sacs.
+papa|Vous avez fini de jouer ?
+enfant-m|Oui, papa.
+enfant-f|Oui.
+papa|Bravo.
+maman|On boit une gorgée ?
+enfant-m|Oui, maman.
+narrateur|La gourde est fraîche, à l'ombre.
+narrateur|Le bois de la palissade est encore chaud.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1872,7 +1951,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le ballon rouge repose près des sacs. Passer. Un tour. L'espace du jeu. Au parc, puis au jardin. Oui, papa. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2012,10 +2091,15 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le ballon rouge repose près des sacs.
+papa|Passer.
+papa|Un tour.
+papa|L'espace du jeu.
+maman|Au parc, puis au jardin.
+enfant-m|Oui, papa.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2034,7 +2118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2156,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.BAL.001-03.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-03.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le ballon rouge s'appuie contre la palissade. Le bois est chaud au soleil. Au loin, un chien dit wouaf, une fois. Les feuilles bougent. Papa marche sur l'herbe courte. Nina attend près du banc. Maman pose la gourde à l'ombre. Nino, tu vois le ballon ? Oui, papa. Il est rouge. Il attend contre le bois. Il est tout chaud, ce bois. En ce moment, papa montre un cercle d'herbe. C'est l'espace du jeu. On reste dans l'espace du jeu. Nino a le ballon rouge. Le grain du ballon pique un peu. Chacun a un tour. On se passe le ballon. Nino passe le ballon à Nina. Nina le passe à papa. C'est le tour de Nino. Il reste dans l'espace du jeu. Bien joué. Chacun a un tour. C'est ton tour, Nino. Je passe. Nino passe encore. Les pieds restent dans l'herbe du cercle. Vous restez dans l'espace. Plus tard, au jardin, papa pose deux sacs. Maman ouvre le portillon. C'est l'espace du jeu. Nino se souvient. Il passe le ballon. Il attend son tour. Puis il joue. Les pieds restent dans l'espace du jeu. Au parc, puis au jardin. Passer. Un tour. L'espace du jeu. Un tour. L'espace du jeu. Chacun a un tour. Bravo, Nino. Bravo, Nina. Vous avez fait du bon travail. Le ballon rouge n'est plus contre la palissade. Il voyage entre les mains.</t>
+          <t>Le ballon rouge s'appuie contre la palissade. Le bois est chaud au soleil. Au loin, un chien dit wouaf, une fois. Les feuilles bougent. Une feuille tombe sur le banc. Papa marche sur l'herbe courte. Nina attend près du banc. Elle touche l'herbe. Maman pose la gourde à l'ombre. Nino, tu vois le ballon ? Oui, papa. Il est rouge. Il attend contre le bois. Il est tout chaud, ce bois. En ce moment, papa montre un cercle d'herbe. C'est l'espace du jeu. On reste dans l'espace du jeu. Nino a le ballon rouge. Le grain du ballon pique un peu. Chacun a un tour. On se passe le ballon. Nino passe le ballon à Nina. Nina le passe à papa. C'est le tour de Nino. Il reste dans l'espace du jeu. Bien joué. Chacun a un tour. C'est ton tour, Nino. Je passe. Nino passe encore. Les pieds restent dans l'herbe du cercle. Vous restez dans l'espace. Plus tard, au jardin, papa pose deux sacs. Maman ouvre le portillon. C'est l'espace du jeu. Nino se souvient. Il passe le ballon. Il attend son tour. Puis il joue. Les pieds restent dans l'espace du jeu. Au parc, puis au jardin. Passer. Un tour. L'espace du jeu. Un tour. L'espace du jeu. Chacun a un tour. Bravo, Nino. Bravo, Nina. Vous avez fait du bon travail. Le ballon rouge n'est plus contre la palissade. Il voyage entre les mains.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sacha est au parc avec papa. Papa montre un cercle d'herbe. Papa dit : c'est l'espace du jeu. On reste dans l'espace du jeu. Sacha a un ballon rouge. Papa dit : chacun a un tour. On se passe le ballon. Sacha passe le ballon à Lina. Lina le passe à papa. C'est le tour de Sacha. Il reste dans l'espace du jeu. Plus tard, au jardin, papa pose deux sacs. C'est l'espace du jeu. Sacha se souvient. Il passe le ballon. Il attend son tour. Puis il joue. Les pieds restent dans l'espace du jeu. Même leçon, autre lieu. &lt;emphasis level="moderate"&gt;passer&lt;/emphasis&gt;. Un tour. L'espace du jeu.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le ballon rouge s'appuie contre la palissade. Le bois est chaud au soleil. Au loin, un chien dit wouaf, une fois. Les feuilles bougent. Une feuille tombe sur le banc. Papa marche sur l'herbe courte. Nina attend près du banc. Elle touche l'herbe. Maman pose la gourde à l'ombre. Nino, tu vois le ballon ? Oui, papa. Il est rouge. Il attend contre le bois. Il est tout chaud, ce bois. En ce moment, papa montre un cercle d'herbe. C'est l'espace du jeu. On reste dans l'espace du jeu. Nino a le ballon rouge. Le grain du ballon pique un peu. Chacun a un tour. On se passe le ballon. Nino passe le ballon à Nina. Nina le passe à papa. C'est le tour de Nino. Il reste dans l'espace du jeu. Bien joué. Chacun a un tour. C'est ton tour, Nino. Je passe. Nino passe encore. Les pieds restent dans l'herbe du cercle. Vous restez dans l'espace. Plus tard, au jardin, papa pose deux sacs. Maman ouvre le portillon. C'est l'espace du jeu. Nino se souvient. Il passe le ballon. Il attend son tour. Puis il joue. Les pieds restent dans l'espace du jeu. Au parc, puis au jardin. Passer. Un tour. L'espace du jeu. Un tour. L'espace du jeu. Chacun a un tour. Bravo, Nino. Bravo, Nina. Vous avez fait du bon travail. Le ballon rouge n'est plus contre la palissade. Il voyage entre les mains.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1328,8 +1328,10 @@
 narrateur|Le bois est chaud au soleil.
 narrateur|Au loin, un chien dit wouaf, une fois.
 narrateur|Les feuilles bougent.
+narrateur|Une feuille tombe sur le banc.
 narrateur|Papa marche sur l'herbe courte.
 narrateur|Nina attend près du banc.
+narrateur|Elle touche l'herbe.
 narrateur|Maman pose la gourde à l'ombre.
 papa|Nino, tu vois le ballon ?
 enfant-m|Oui, papa.
@@ -1410,7 +1412,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sacha a le ballon. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino a le ballon. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1589,12 +1591,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nino a passé le ballon. Au parc, puis au jardin. Dans l'espace du jeu. Chacun a eu un tour. Tu as attendu ton tour ? Oui, papa. Moi aussi. Bravo. On reste dans l'espace du jeu. Nina, tu as passé aussi ? Oui, maman. Bravo. L'herbe du jardin sent la menthe. Les sacs marquent encore le cercle.</t>
+          <t>Nino a passé le ballon. Au parc, puis au jardin. Dans l'espace du jeu. Chacun a eu un tour. Tu as attendu ton tour ? Oui, papa. Moi aussi. Bravo. On reste dans l'espace du jeu. Nina, tu as passé aussi ? Oui, maman. Bravo. L'herbe du jardin sent la menthe. Les sacs marquent encore le cercle. On reprend un tour ? Oui, papa. Moi aussi. Nino passe. Nina attend, puis elle passe.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sacha a passé le ballon. Au parc, puis au jardin. Dans l'espace du jeu. Chacun a eu un &lt;emphasis level="moderate"&gt;tour&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino a passé le ballon. Au parc, puis au jardin. Dans l'espace du jeu. Chacun a eu un tour. Tu as attendu ton tour ? Oui, papa. Moi aussi. Bravo. On reste dans l'espace du jeu. Nina, tu as passé aussi ? Oui, maman. Bravo. L'herbe du jardin sent la menthe. Les sacs marquent encore le cercle. On reprend un tour ? Oui, papa. Moi aussi. Nino passe. Nina attend, puis elle passe.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1746,7 +1748,12 @@
 enfant-f|Oui, maman.
 maman|Bravo.
 narrateur|L'herbe du jardin sent la menthe.
-narrateur|Les sacs marquent encore le cercle.</t>
+narrateur|Les sacs marquent encore le cercle.
+papa|On reprend un tour ?
+enfant-m|Oui, papa.
+enfant-f|Moi aussi.
+narrateur|Nino passe.
+narrateur|Nina attend, puis elle passe.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1783,7 +1790,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sacha pose le ballon. Papa range les sacs.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino pose le ballon. Je range les sacs. Papa range les sacs. Vous avez fini de jouer ? Oui, papa. Oui. Bravo. On boit une gorgée ? Oui, maman. La gourde est fraîche, à l'ombre. Le bois de la palissade est encore chaud.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1951,12 +1958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le ballon rouge repose près des sacs. Passer. Un tour. L'espace du jeu. Au parc, puis au jardin. Oui, papa. L'histoire est finie.</t>
+          <t>Le ballon rouge repose près des sacs. Passer. Un tour. L'espace du jeu. Au parc, puis au jardin. Oui, papa.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le ballon rouge repose près des sacs. Passer. Un tour. L'espace du jeu. Au parc, puis au jardin. Oui, papa.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2096,8 +2103,7 @@
 papa|Un tour.
 papa|L'espace du jeu.
 maman|Au parc, puis au jardin.
-enfant-m|Oui, papa.
-narrateur|L'histoire est finie.</t>
+enfant-m|Oui, papa.</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2163,6 +2169,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.BAL.001-03.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-03.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>parc puis jardin</t>
+          <t>parc puis jardin, palissade, deux sacs</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sacha, Lina, papa</t>
+          <t>Nino, Nina, papa, maman</t>
         </is>
       </c>
     </row>
